--- a/Sunscape_Missing_Assets.xlsx
+++ b/Sunscape_Missing_Assets.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Missing 3D Models'!$A$4:$K$140</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Missing 2D Images'!$A$4:$J$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Missing 2D Images'!$A$4:$J$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fix Requests'!$A$3:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,11 +538,11 @@
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIF('Missing 2D Images'!$B$5:$B$182,A5)</f>
+        <f>COUNTIF('Missing 2D Images'!$B$5:$B$133,A5)</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$182,A5,'Missing 2D Images'!$J$5:$J$182,"Yes")</f>
+        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$133,A5,'Missing 2D Images'!$J$5:$J$133,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -561,11 +561,11 @@
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>COUNTIF('Missing 2D Images'!$B$5:$B$182,A6)</f>
+        <f>COUNTIF('Missing 2D Images'!$B$5:$B$133,A6)</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$182,A6,'Missing 2D Images'!$J$5:$J$182,"Yes")</f>
+        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$133,A6,'Missing 2D Images'!$J$5:$J$133,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -584,11 +584,11 @@
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>COUNTIF('Missing 2D Images'!$B$5:$B$182,A7)</f>
+        <f>COUNTIF('Missing 2D Images'!$B$5:$B$133,A7)</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$182,A7,'Missing 2D Images'!$J$5:$J$182,"Yes")</f>
+        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$133,A7,'Missing 2D Images'!$J$5:$J$133,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -607,11 +607,11 @@
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>COUNTIF('Missing 2D Images'!$B$5:$B$182,A8)</f>
+        <f>COUNTIF('Missing 2D Images'!$B$5:$B$133,A8)</f>
         <v/>
       </c>
       <c r="E8" s="4">
-        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$182,A8,'Missing 2D Images'!$J$5:$J$182,"Yes")</f>
+        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$133,A8,'Missing 2D Images'!$J$5:$J$133,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -630,11 +630,11 @@
         <v/>
       </c>
       <c r="D9" s="4">
-        <f>COUNTIF('Missing 2D Images'!$B$5:$B$182,A9)</f>
+        <f>COUNTIF('Missing 2D Images'!$B$5:$B$133,A9)</f>
         <v/>
       </c>
       <c r="E9" s="4">
-        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$182,A9,'Missing 2D Images'!$J$5:$J$182,"Yes")</f>
+        <f>COUNTIFS('Missing 2D Images'!$B$5:$B$133,A9,'Missing 2D Images'!$J$5:$J$133,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7825,1453 +7825,1453 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Sink Base Cabinets</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>SBC3C45</t>
+          <t>ADA44BC</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>SBC3C45</t>
+          <t>ADA44BC</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>SBC3C45.webp</t>
+          <t>ADA44BC.webp</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SBC3C45/2d/</t>
+          <t>public/assets/cabinet-islands/sink-base-cabinets/ADA44BC/2d/</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Counter Bar</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>SCC15SPE-W</t>
+          <t>ISLAND_45ANGLE_COUNTERBAR</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>SCC15SPE-W</t>
+          <t>ISLAND_45ANGLE_COUNTERBAR</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>SCC15SPE-W.webp</t>
+          <t>ISLAND_45ANGLE_COUNTERBAR.webp</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC15SPE-W/2d/</t>
+          <t>public/assets/island-modules/counter-bar/ISLAND_45ANGLE_COUNTERBAR/2d/</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Counter Bar</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SCC21SPE-W</t>
+          <t>ISLAND_COUNTERBAR_CORNER</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>SCC21SPE-W</t>
+          <t>ISLAND_COUNTERBAR_CORNER_LEFT</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>SCC21SPE-W.webp</t>
+          <t>ISLAND_COUNTERBAR_CORNER_LEFT.webp</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC21SPE-W/2d/</t>
+          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_CORNER/2d/</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Counter Bar</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>SCC25SPE-W</t>
+          <t>ISLAND_COUNTERBAR_CORNER</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>SCC25SPE-W</t>
+          <t>ISLAND_COUNTERBAR_CORNER_RIGHT</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>SCC25SPE-W.webp</t>
+          <t>ISLAND_COUNTERBAR_CORNER_RIGHT.webp</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC25SPE-W/2d/</t>
+          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_CORNER/2d/</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Counter Bar</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>SCC27EP</t>
+          <t>ISLAND_COUNTERBAR_ENDCAP</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>SCC27EP_SCC25KP_LEFT</t>
+          <t>ISLAND_COUNTERBAR_ENDCAP_LEFT</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>SCC27EP_SCC25KP_LEFT.webp</t>
+          <t>ISLAND_COUNTERBAR_ENDCAP_LEFT.webp</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC27EP/2d/</t>
+          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_ENDCAP/2d/</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Counter Bar</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>SCC27EP</t>
+          <t>ISLAND_COUNTERBAR_ENDCAP</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>SCC27EP_SCC25KP_RIGHT</t>
+          <t>ISLAND_COUNTERBAR_ENDCAP_RIGHT</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>SCC27EP_SCC25KP_RIGHT.webp</t>
+          <t>ISLAND_COUNTERBAR_ENDCAP_RIGHT.webp</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC27EP/2d/</t>
+          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_ENDCAP/2d/</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Counter Bar</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>SCC31BP90</t>
+          <t>ISLAND_COUNTERBAR_STRAIGHT_12</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>SCC31BP90</t>
+          <t>ISLAND_COUNTERBAR_STRAIGHT_12</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>SCC31BP90.webp</t>
+          <t>ISLAND_COUNTERBAR_STRAIGHT_12.webp</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC31BP90/2d/</t>
+          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_STRAIGHT_12/2d/</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Grill Jacket Packages</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>SCC31BP90</t>
+          <t>ISLAND_SUNJK18_22</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>SCC31BP90_ASS17</t>
+          <t>ISLAND_SUNJK18_22</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>SCC31BP90_ASS17.webp</t>
+          <t>ISLAND_SUNJK18_22.webp</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC31BP90/2d/</t>
+          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK18_22/2d/</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Grill Jacket Packages</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>SCC3CSP</t>
+          <t>ISLAND_SUNJK29_34</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>SCC3CSP</t>
+          <t>ISLAND_SUNJK29_34</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SCC3CSP.webp</t>
+          <t>ISLAND_SUNJK29_34.webp</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC3CSP/2d/</t>
+          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK29_34/2d/</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Grill Jacket Packages</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>SCC3ENDSPL</t>
+          <t>ISLAND_SUNJK33_40</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>SCC3ENDSPL_LEFT</t>
+          <t>ISLAND_SUNJK33_40</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>SCC3ENDSPL_LEFT.webp</t>
+          <t>ISLAND_SUNJK33_40.webp</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC3ENDSPL/2d/</t>
+          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK33_40/2d/</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Grill Jacket Packages</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>SCC3ENDSPR</t>
+          <t>ISLAND_SUNJK40_46</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>SCC3ENDSPR_RIGHT</t>
+          <t>ISLAND_SUNJK40_46</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>SCC3ENDSPR_RIGHT.webp</t>
+          <t>ISLAND_SUNJK40_46.webp</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC3ENDSPR/2d/</t>
+          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK40_46/2d/</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Grill Jacket Packages</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90</t>
+          <t>ISLAND_SUNJK45_50</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90</t>
+          <t>ISLAND_SUNJK45_50</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90.webp</t>
+          <t>ISLAND_SUNJK45_50.webp</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC3SP90/2d/</t>
+          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK45_50/2d/</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Grill Jacket Packages</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90</t>
+          <t>SUNJK33</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90_ASS17</t>
+          <t>SUNJK33_SUNCHSZ30_POST</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90_ASS17.webp</t>
+          <t>SUNJK33_SUNCHSZ30_POST.webp</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC3SP90/2d/</t>
+          <t>public/assets/island-modules/grill-jacket-packages/SUNJK33/2d/</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90</t>
+          <t>ISLAND_45ANGLE_RAISEDBAR</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90_SUN13VSB</t>
+          <t>ISLAND_45ANGLE_RAISEDBAR</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>SCC3SP90_SUN13VSB.webp</t>
+          <t>ISLAND_45ANGLE_RAISEDBAR.webp</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC3SP90/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_45ANGLE_RAISEDBAR/2d/</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>SCC3SPF</t>
+          <t>ISLAND_90CORNER_RAISEDBAR</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>SCC3SPF_SCC3SPB</t>
+          <t>ISLAND_90CORNER_RAISEDBAR</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>SCC3SPF_SCC3SPB.webp</t>
+          <t>ISLAND_90CORNER_RAISEDBAR.webp</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC3SPF/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_90CORNER_RAISEDBAR/2d/</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>SCC4SPEL</t>
+          <t>ISLAND_RAISEDBAR_24</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>SCC4SPEL</t>
+          <t>ISLAND_RAISEDBAR_24</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>SCC4SPEL.webp</t>
+          <t>ISLAND_RAISEDBAR_24.webp</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC4SPEL/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_24/2d/</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>SCC4SPER</t>
+          <t>ISLAND_RAISEDBAR_ROUNDEND</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>SCC4SPER</t>
+          <t>ISLAND_RAISEDBAR_ROUNDEND_LEFT</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>SCC4SPER.webp</t>
+          <t>ISLAND_RAISEDBAR_ROUNDEND_LEFT.webp</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC4SPER/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_ROUNDEND/2d/</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Component Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>SCC6SPF</t>
+          <t>ISLAND_RAISEDBAR_ROUNDEND</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>SCC6SPF_SCC6SPB</t>
+          <t>ISLAND_RAISEDBAR_ROUNDEND_RIGHT</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>SCC6SPF_SCC6SPB.webp</t>
+          <t>ISLAND_RAISEDBAR_ROUNDEND_RIGHT.webp</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/component-cabinets/SCC6SPF/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_ROUNDEND/2d/</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDL</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_12</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDL_BCS14</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_12</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDL_BCS14.webp</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_12.webp</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC20CSDL/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_12/2d/</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDL</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_24</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDL_SUN13VDSB</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_24</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDL_SUN13VDSB.webp</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_24.webp</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC20CSDL/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_24/2d/</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDR</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_36</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDR_BCS14</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_36</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDR_BCS14.webp</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_36.webp</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC20CSDR/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_36/2d/</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDR</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_48</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDR_SUN13VDSB</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_48</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>SAC20CSDR_SUN13VDSB.webp</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_48.webp</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC20CSDR/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_48/2d/</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>SAC30KBDC</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>SAC30KBDC</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>SAC30KBDC.webp</t>
+          <t>ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END.webp</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC30KBDC/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END/2d/</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Raised Bar</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>SAC30KBDC</t>
+          <t>ISLAND_RAISED_CURVED_BAR_8FT</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>SAC30KBDC_KAMADO_SHORT</t>
+          <t>ISLAND_RAISED_CURVED_BAR_8FT</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>SAC30KBDC_KAMADO_SHORT.webp</t>
+          <t>ISLAND_RAISED_CURVED_BAR_8FT.webp</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC30KBDC/2d/</t>
+          <t>public/assets/island-modules/raised-bar/ISLAND_RAISED_CURVED_BAR_8FT/2d/</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>SAC33PBDC</t>
+          <t>ISLAND_45ANGLE_3X3</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>SAC33PBDC</t>
+          <t>ISLAND_45ANGLE_3X3</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>SAC33PBDC.webp</t>
+          <t>ISLAND_45ANGLE_3X3.webp</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC33PBDC/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_45ANGLE_3X3/2d/</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>SAC34CGDC</t>
+          <t>ISLAND_90CORNER</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>SAC34CGDC_SUNCHSZ30IR</t>
+          <t>ISLAND_90CORNER</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>SAC34CGDC_SUNCHSZ30IR.webp</t>
+          <t>ISLAND_90CORNER.webp</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC34CGDC/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_90CORNER/2d/</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>SAC40GLPCD</t>
+          <t>ISLAND_ASS17_19</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>SAC40GLPCD_RUBY4BIR</t>
+          <t>ISLAND_ASS17_19</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>SAC40GLPCD_RUBY4BIR.webp</t>
+          <t>ISLAND_ASS17_19.webp</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC40GLPCD/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_ASS17_19/2d/</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>SAC46CGDC</t>
+          <t>ISLAND_BIC14_15</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>SAC46CGDC_EMCHDZ42</t>
+          <t>ISLAND_BIC14_15</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>SAC46CGDC_EMCHDZ42.webp</t>
+          <t>ISLAND_BIC14_15.webp</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SAC46CGDC/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_BIC14_15/2d/</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>SBC34DWC</t>
+          <t>ISLAND_BPS21_24</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>SBC34DWC</t>
+          <t>ISLAND_BPS21_24</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>SBC34DWC.webp</t>
+          <t>ISLAND_BPS21_24.webp</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SBC34DWC/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_BPS21_24/2d/</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Grill Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>SBC34WDPC</t>
+          <t>ISLAND_BSK20_22</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>SBC34WDPC</t>
+          <t>ISLAND_BSK20_22</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>SBC34WDPC.webp</t>
+          <t>ISLAND_BSK20_22.webp</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/grill-cabinets/SBC34WDPC/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_BSK20_22/2d/</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Sink Base Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>ADA44BA</t>
+          <t>ISLAND_BSK34_35</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>ADA44BA_ADASK37</t>
+          <t>ISLAND_BSK34_35</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>ADA44BA_ADASK37.webp</t>
+          <t>ISLAND_BSK34_35.webp</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/sink-base-cabinets/ADA44BA/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_BSK34_35/2d/</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Sink Base Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>ADA44BC</t>
+          <t>ISLAND_ENDCAP</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>ADA44BC</t>
+          <t>ISLAND_ENDCAP_LEFT</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>ADA44BC.webp</t>
+          <t>ISLAND_ENDCAP_LEFT.webp</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/sink-base-cabinets/ADA44BC/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP/2d/</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -9288,828 +9288,828 @@
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Sink Base Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>SBC36CDD</t>
+          <t>ISLAND_ENDCAP</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>SBC36CDD_SK34</t>
+          <t>ISLAND_ENDCAP_RIGHT</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>SBC36CDD_SK34.webp</t>
+          <t>ISLAND_ENDCAP_RIGHT.webp</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/sink-base-cabinets/SBC36CDD/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP/2d/</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Sink Base Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>SBC36FDD</t>
+          <t>ISLAND_ENDCAP_TOBAR</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>SBC36FDD_BPS21</t>
+          <t>ISLAND_ENDCAP_TOBAR_LEFT</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>SBC36FDD_BPS21.webp</t>
+          <t>ISLAND_ENDCAP_TOBAR_LEFT.webp</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/sink-base-cabinets/SBC36FDD/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP_TOBAR/2d/</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Sink Base Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>SBC36FDD</t>
+          <t>ISLAND_ENDCAP_TOBAR</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>SBC36FDD_SK34</t>
+          <t>ISLAND_ENDCAP_TOBAR_RIGHT</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>SBC36FDD_SK34.webp</t>
+          <t>ISLAND_ENDCAP_TOBAR_RIGHT.webp</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/sink-base-cabinets/SBC36FDD/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP_TOBAR/2d/</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Storage Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>SBC12SLS</t>
+          <t>ISLAND_ROUND_END</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>SBC12SLS</t>
+          <t>ISLAND_ROUND_END_LEFT</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>SBC12SLS.webp</t>
+          <t>ISLAND_ROUND_END_LEFT.webp</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/storage-cabinets/SBC12SLS/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_ROUND_END/2d/</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Storage Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>SBC12SMD</t>
+          <t>ISLAND_ROUND_END</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>SBC12SMD</t>
+          <t>ISLAND_ROUND_END_RIGHT</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>SBC12SMD.webp</t>
+          <t>ISLAND_ROUND_END_RIGHT.webp</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/storage-cabinets/SBC12SMD/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_ROUND_END/2d/</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>SWC12SLS</t>
+          <t>ISLAND_SAPFR21PRO_BATRIM21_26</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>SWC12SLS</t>
+          <t>ISLAND_SAPFR21PRO_BATRIM21_26</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SWC12SLS.webp</t>
+          <t>ISLAND_SAPFR21PRO_BATRIM21_26.webp</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC12SLS/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_SAPFR21PRO_BATRIM21_26/2d/</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>SWC18CSDL</t>
+          <t>ISLAND_SCC3ENDSPL</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>SWC18CSDL</t>
+          <t>ISLAND_SCC3ENDSPL_LEFT</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>SWC18CSDL.webp</t>
+          <t>ISLAND_SCC3ENDSPL_LEFT.webp</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC18CSDL/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_SCC3ENDSPL/2d/</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>SWC18CSDR</t>
+          <t>ISLAND_STRAIGHT_12</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>SWC18CSDR</t>
+          <t>ISLAND_STRAIGHT_12</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>SWC18CSDR.webp</t>
+          <t>ISLAND_STRAIGHT_12.webp</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC18CSDR/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_12/2d/</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>SWC18FSDL</t>
+          <t>ISLAND_STRAIGHT_24</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>SWC18FSDL</t>
+          <t>ISLAND_STRAIGHT_24</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>SWC18FSDL.webp</t>
+          <t>ISLAND_STRAIGHT_24.webp</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC18FSDL/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_24/2d/</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>SWC18FSDR</t>
+          <t>ISLAND_STRAIGHT_36</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>SWC18FSDR</t>
+          <t>ISLAND_STRAIGHT_36</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>SWC18FSDR.webp</t>
+          <t>ISLAND_STRAIGHT_36.webp</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC18FSDR/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_36/2d/</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>SWC21EP</t>
+          <t>ISLAND_STRAIGHT_48</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>SWC21EP_LEFT</t>
+          <t>ISLAND_STRAIGHT_48</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>SWC21EP_LEFT.webp</t>
+          <t>ISLAND_STRAIGHT_48.webp</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC21EP/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_48/2d/</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Straight &amp; Ends</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>SWC21EP</t>
+          <t>ISLAND_STRAIGHT_OVERHANG_12</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>SWC21EP_RIGHT</t>
+          <t>ISLAND_STRAIGHT_OVERHANG_12</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>SWC21EP_RIGHT.webp</t>
+          <t>ISLAND_STRAIGHT_OVERHANG_12.webp</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC21EP/2d/</t>
+          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_OVERHANG_12/2d/</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>SWC24FDD</t>
+          <t>ISLAND_BAR_ROUND_36_STUCCO</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>SWC24FDD</t>
+          <t>ISLAND_BAR_ROUND_36_STUCCO</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>SWC24FDD.webp</t>
+          <t>ISLAND_BAR_ROUND_36_STUCCO.webp</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC24FDD/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_BAR_ROUND_36_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>SWC30FDD</t>
+          <t>ISLAND_CORONADO_CORNER_4X4_STUCCO</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>SWC30FDD</t>
+          <t>ISLAND_CORONADO_CORNER_4X4_STUCCO</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>SWC30FDD.webp</t>
+          <t>ISLAND_CORONADO_CORNER_4X4_STUCCO.webp</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC30FDD/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_CORNER_4X4_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>SWC36FDD</t>
+          <t>ISLAND_CORONADO_EXTEND_24_STUCCO</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>SWC36FDD</t>
+          <t>ISLAND_CORONADO_EXTEND_24_STUCCO</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>SWC36FDD.webp</t>
+          <t>ISLAND_CORONADO_EXTEND_24_STUCCO.webp</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC36FDD/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_EXTEND_24_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>SWC3SP90</t>
+          <t>ISLAND_CORONADO_L_6FT_STUCCO</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>SWC3SP90</t>
+          <t>ISLAND_CORONADO_L_6FT_STUCCO</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>SWC3SP90.webp</t>
+          <t>ISLAND_CORONADO_L_6FT_STUCCO.webp</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC3SP90/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_L_6FT_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>SWC42EP</t>
+          <t>ISLAND_CORONADO_R_6FT_STUCCO</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>SWC42EP_LEFT</t>
+          <t>ISLAND_CORONADO_R_6FT_STUCCO</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>SWC42EP_LEFT.webp</t>
+          <t>ISLAND_CORONADO_R_6FT_STUCCO.webp</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC42EP/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_R_6FT_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Cabinet Islands</t>
+          <t>Island Modules</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Wall Cabinets</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>SWC42EP</t>
+          <t>ISLAND_RAISED_45_ANGLE_STUCCO</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>SWC42EP_RIGHT</t>
+          <t>ISLAND_RAISED_45_ANGLE_STUCCO</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>SWC42EP_RIGHT.webp</t>
+          <t>ISLAND_RAISED_45_ANGLE_STUCCO.webp</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>public/assets/cabinet-islands/wall-cabinets/SWC42EP/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_45_ANGLE_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Real 3D model on file</t>
+          <t>No 3D model yet</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Can be auto-rendered from the 3D model</t>
+          <t>Needs artwork or a 3D model</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr"/>
@@ -10125,27 +10125,27 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Counter Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_COUNTERBAR</t>
+          <t>ISLAND_RAISED_L_CORNER_30x48_STUCCO</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_COUNTERBAR</t>
+          <t>ISLAND_RAISED_L_CORNER_30x48_STUCCO</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_COUNTERBAR.webp</t>
+          <t>ISLAND_RAISED_L_CORNER_30x48_STUCCO.webp</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/counter-bar/ISLAND_45ANGLE_COUNTERBAR/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_L_CORNER_30x48_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -10171,27 +10171,27 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Counter Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_CORNER</t>
+          <t>ISLAND_RAISED_L_LANDING_4FT_STUCCO</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_CORNER_LEFT</t>
+          <t>ISLAND_RAISED_L_LANDING_4FT_STUCCO</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_CORNER_LEFT.webp</t>
+          <t>ISLAND_RAISED_L_LANDING_4FT_STUCCO.webp</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_CORNER/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_L_LANDING_4FT_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -10217,27 +10217,27 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Counter Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_CORNER</t>
+          <t>ISLAND_RAISED_L_ROUND_4FT_STUCCO</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_CORNER_RIGHT</t>
+          <t>ISLAND_RAISED_L_ROUND_4FT_STUCCO</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_CORNER_RIGHT.webp</t>
+          <t>ISLAND_RAISED_L_ROUND_4FT_STUCCO.webp</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_CORNER/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_L_ROUND_4FT_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -10263,27 +10263,27 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Counter Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_ENDCAP</t>
+          <t>ISLAND_RAISED_R_CORNER_30x48_STUCCO</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_ENDCAP_LEFT</t>
+          <t>ISLAND_RAISED_R_CORNER_30x48_STUCCO</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_ENDCAP_LEFT.webp</t>
+          <t>ISLAND_RAISED_R_CORNER_30x48_STUCCO.webp</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_ENDCAP/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_R_CORNER_30x48_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -10309,27 +10309,27 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Counter Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_ENDCAP</t>
+          <t>ISLAND_RAISED_R_LANDING_4FT_STUCCO</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_ENDCAP_RIGHT</t>
+          <t>ISLAND_RAISED_R_LANDING_4FT_STUCCO</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_ENDCAP_RIGHT.webp</t>
+          <t>ISLAND_RAISED_R_LANDING_4FT_STUCCO.webp</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_ENDCAP/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_R_LANDING_4FT_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -10355,27 +10355,27 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Counter Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_STRAIGHT_12</t>
+          <t>ISLAND_RAISED_R_ROUND_4FT_STUCCO</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_STRAIGHT_12</t>
+          <t>ISLAND_RAISED_R_ROUND_4FT_STUCCO</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_COUNTERBAR_STRAIGHT_12.webp</t>
+          <t>ISLAND_RAISED_R_ROUND_4FT_STUCCO.webp</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/counter-bar/ISLAND_COUNTERBAR_STRAIGHT_12/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_R_ROUND_4FT_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Grill Jacket Packages</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK18_22</t>
+          <t>ISLAND_RAISED_STRAIGHT_24_STUCCO</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK18_22</t>
+          <t>ISLAND_RAISED_STRAIGHT_24_STUCCO</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK18_22.webp</t>
+          <t>ISLAND_RAISED_STRAIGHT_24_STUCCO.webp</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK18_22/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_STRAIGHT_24_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -10447,27 +10447,27 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Grill Jacket Packages</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK29_34</t>
+          <t>ISLAND_STCROIX_8FT_STUCCO</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK29_34</t>
+          <t>ISLAND_STCROIX_8FT_STUCCO</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK29_34.webp</t>
+          <t>ISLAND_STCROIX_8FT_STUCCO.webp</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK29_34/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STCROIX_8FT_STUCCO/2d/</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -10493,27 +10493,27 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Grill Jacket Packages</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK33_40</t>
+          <t>ISLAND_STUCCO_CORNER_FIREPLACE</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK33_40</t>
+          <t>ISLAND_STUCCO_CORNER_FIREPLACE</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK33_40.webp</t>
+          <t>ISLAND_STUCCO_CORNER_FIREPLACE.webp</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK33_40/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_CORNER_FIREPLACE/2d/</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -10539,27 +10539,27 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Grill Jacket Packages</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK40_46</t>
+          <t>ISLAND_STUCCO_KAMADOBASE_30</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK40_46</t>
+          <t>ISLAND_STUCCO_KAMADOBASE_30</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK40_46.webp</t>
+          <t>ISLAND_STUCCO_KAMADOBASE_30.webp</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK40_46/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_KAMADOBASE_30/2d/</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
@@ -10585,27 +10585,27 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Grill Jacket Packages</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK45_50</t>
+          <t>ISLAND_STUCCO_LOWBASE</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK45_50</t>
+          <t>ISLAND_STUCCO_LOWBASE_LEFT</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SUNJK45_50.webp</t>
+          <t>ISLAND_STUCCO_LOWBASE_LEFT.webp</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/grill-jacket-packages/ISLAND_SUNJK45_50/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_LOWBASE/2d/</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
@@ -10631,27 +10631,27 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Grill Jacket Packages</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>SUNJK33</t>
+          <t>ISLAND_STUCCO_LOWBASE</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>SUNJK33_SUNCHSZ30_POST</t>
+          <t>ISLAND_STUCCO_LOWBASE_RIGHT</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>SUNJK33_SUNCHSZ30_POST.webp</t>
+          <t>ISLAND_STUCCO_LOWBASE_RIGHT.webp</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/grill-jacket-packages/SUNJK33/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_LOWBASE/2d/</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
@@ -10677,27 +10677,27 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_RAISEDBAR</t>
+          <t>ISLAND_STUCCO_OVERHANG_12</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_RAISEDBAR</t>
+          <t>ISLAND_STUCCO_OVERHANG_12</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_RAISEDBAR.webp</t>
+          <t>ISLAND_STUCCO_OVERHANG_12.webp</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_45ANGLE_RAISEDBAR/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_OVERHANG_12/2d/</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
@@ -10723,27 +10723,27 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_90CORNER_RAISEDBAR</t>
+          <t>ISLAND_STUCCO_SCC3ENDSPL</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_90CORNER_RAISEDBAR</t>
+          <t>ISLAND_STUCCO_SCC3ENDSPL_LEFT</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_90CORNER_RAISEDBAR.webp</t>
+          <t>ISLAND_STUCCO_SCC3ENDSPL_LEFT.webp</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_90CORNER_RAISEDBAR/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_SCC3ENDSPL/2d/</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -10769,27 +10769,27 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Stucco / Masonry</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_24</t>
+          <t>ISLAND_STUCCO_SCC3ENDSPL</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_24</t>
+          <t>ISLAND_STUCCO_SCC3ENDSPL_RIGHT</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_24.webp</t>
+          <t>ISLAND_STUCCO_SCC3ENDSPL_RIGHT.webp</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_24/2d/</t>
+          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_SCC3ENDSPL/2d/</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
@@ -10806,36 +10806,36 @@
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>ADA Compliant Sinks</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_ROUNDEND</t>
+          <t>ADASK20</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_ROUNDEND_LEFT</t>
+          <t>ADASK20</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_ROUNDEND_LEFT.webp</t>
+          <t>ADASK20.webp</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_ROUNDEND/2d/</t>
+          <t>public/assets/appliances/ada-compliant-sinks/ADASK20/2d/</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -10852,36 +10852,36 @@
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>ADA Compliant Sinks</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_ROUNDEND</t>
+          <t>ADASK37</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_ROUNDEND_RIGHT</t>
+          <t>ADASK37</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_ROUNDEND_RIGHT.webp</t>
+          <t>ADASK37.webp</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_ROUNDEND/2d/</t>
+          <t>public/assets/appliances/ada-compliant-sinks/ADASK37/2d/</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -10898,36 +10898,36 @@
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Appliance Components</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_12</t>
+          <t>BC_BC14</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_12</t>
+          <t>BC_BC14</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_12.webp</t>
+          <t>BC_BC14.webp</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_12/2d/</t>
+          <t>public/assets/appliances/appliance-components/BC_BC14/2d/</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -10944,36 +10944,36 @@
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Appliance Components</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_24</t>
+          <t>BC_TD14</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_24</t>
+          <t>BC_TD14</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_24.webp</t>
+          <t>BC_TD14.webp</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_24/2d/</t>
+          <t>public/assets/appliances/appliance-components/BC_TD14/2d/</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
@@ -10990,36 +10990,36 @@
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Appliance Components</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_36</t>
+          <t>BRBC14</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_36</t>
+          <t>BRBC14</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_36.webp</t>
+          <t>BRBC14.webp</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_36/2d/</t>
+          <t>public/assets/appliances/appliance-components/BRBC14/2d/</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
@@ -11036,36 +11036,36 @@
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Refrigeration &amp; Warming</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_48</t>
+          <t>SAPFR21PRO</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_48</t>
+          <t>SAPFR21PRO</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_48.webp</t>
+          <t>SAPFR21PRO.webp</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_48/2d/</t>
+          <t>public/assets/appliances/refrigeration-warming/SAPFR21PRO/2d/</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
@@ -11082,36 +11082,36 @@
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Refrigeration &amp; Warming</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END</t>
+          <t>SAPFR21PRO</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END</t>
+          <t>SAPFR21PRO_BATRIM21</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END.webp</t>
+          <t>SAPFR21PRO_BATRIM21.webp</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISEDBAR_STRAIGHT_RIGHT_END/2d/</t>
+          <t>public/assets/appliances/refrigeration-warming/SAPFR21PRO/2d/</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -11128,36 +11128,36 @@
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Raised Bar</t>
+          <t>Refrigeration &amp; Warming</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_CURVED_BAR_8FT</t>
+          <t>SAPWD30PRO</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_CURVED_BAR_8FT</t>
+          <t>SAPWD30PRO</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_CURVED_BAR_8FT.webp</t>
+          <t>SAPWD30PRO.webp</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/raised-bar/ISLAND_RAISED_CURVED_BAR_8FT/2d/</t>
+          <t>public/assets/appliances/refrigeration-warming/SAPWD30PRO/2d/</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
@@ -11174,36 +11174,36 @@
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Appliances &amp; Sinks</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Refrigeration &amp; Warming</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_3X3</t>
+          <t>SAPWD30PRO</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_3X3</t>
+          <t>SAPWD30PRO_DE</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_45ANGLE_3X3.webp</t>
+          <t>SAPWD30PRO_DE.webp</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_45ANGLE_3X3/2d/</t>
+          <t>public/assets/appliances/refrigeration-warming/SAPWD30PRO/2d/</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
@@ -11220,36 +11220,36 @@
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Charcoal Combo Grillers</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_90CORNER</t>
+          <t>SUNCHDZ42</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_90CORNER</t>
+          <t>SUNCHDZ42</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_90CORNER.webp</t>
+          <t>SUNCHDZ42.webp</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_90CORNER/2d/</t>
+          <t>public/assets/outdoor-cooking/charcoal-combo-grillers/SUNCHDZ42/2d/</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
@@ -11266,36 +11266,36 @@
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Charcoal Combo Grillers</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ASS17_19</t>
+          <t>SUNCHSZ30</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ASS17_19</t>
+          <t>SUNCHSZ30</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ASS17_19.webp</t>
+          <t>SUNCHSZ30.webp</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_ASS17_19/2d/</t>
+          <t>public/assets/outdoor-cooking/charcoal-combo-grillers/SUNCHSZ30/2d/</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
@@ -11312,36 +11312,36 @@
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Grill Components</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BIC14_15</t>
+          <t>VENT</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BIC14_15</t>
+          <t>VENT_GBOX</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BIC14_15.webp</t>
+          <t>VENT_GBOX.webp</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_BIC14_15/2d/</t>
+          <t>public/assets/outdoor-cooking/grill-components/VENT/2d/</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
@@ -11358,36 +11358,36 @@
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Grill Components</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BPS21_24</t>
+          <t>VENT</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BPS21_24</t>
+          <t>VENT_L</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BPS21_24.webp</t>
+          <t>VENT_L.webp</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_BPS21_24/2d/</t>
+          <t>public/assets/outdoor-cooking/grill-components/VENT/2d/</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
@@ -11404,36 +11404,36 @@
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Grill Components</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BSK20_22</t>
+          <t>VENT</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BSK20_22</t>
+          <t>VENT_S</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BSK20_22.webp</t>
+          <t>VENT_S.webp</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_BSK20_22/2d/</t>
+          <t>public/assets/outdoor-cooking/grill-components/VENT/2d/</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
@@ -11450,36 +11450,36 @@
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Pellet Grills</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BSK34_35</t>
+          <t>SUNPLT40</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BSK34_35</t>
+          <t>SUNPLT40</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BSK34_35.webp</t>
+          <t>SUNPLT40.webp</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_BSK34_35/2d/</t>
+          <t>public/assets/outdoor-cooking/pellet-grills/SUNPLT40/2d/</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
@@ -11496,36 +11496,36 @@
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Power Cirque Burners &amp; Griddles</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP</t>
+          <t>SUN24PCB</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_LEFT</t>
+          <t>SUN24PCB_GD</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_LEFT.webp</t>
+          <t>SUN24PCB_GD.webp</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP/2d/</t>
+          <t>public/assets/outdoor-cooking/power-burners-griddles/SUN24PCB/2d/</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
@@ -11542,36 +11542,36 @@
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Power Cirque Burners &amp; Griddles</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP</t>
+          <t>SUN24PCB</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_RIGHT</t>
+          <t>SUN24PCB_PB</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_RIGHT.webp</t>
+          <t>SUN24PCB_PB.webp</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP/2d/</t>
+          <t>public/assets/outdoor-cooking/power-burners-griddles/SUN24PCB/2d/</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -11588,36 +11588,36 @@
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Ruby Gas Grills</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_TOBAR</t>
+          <t>RUBY3B</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_TOBAR_LEFT</t>
+          <t>RUBY3B_30</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_TOBAR_LEFT.webp</t>
+          <t>RUBY3B_30.webp</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP_TOBAR/2d/</t>
+          <t>public/assets/outdoor-cooking/gas-grills/RUBY3B/2d/</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
@@ -11634,36 +11634,36 @@
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Ruby Gas Grills</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_TOBAR</t>
+          <t>RUBY4B</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_TOBAR_RIGHT</t>
+          <t>RUBY4B_36</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ENDCAP_TOBAR_RIGHT.webp</t>
+          <t>RUBY4B_36.webp</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_ENDCAP_TOBAR/2d/</t>
+          <t>public/assets/outdoor-cooking/gas-grills/RUBY4B/2d/</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
@@ -11680,36 +11680,36 @@
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Ruby Gas Grills</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ROUND_END</t>
+          <t>RUBY4BIR</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ROUND_END_LEFT</t>
+          <t>RUBY4BIR_36</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ROUND_END_LEFT.webp</t>
+          <t>RUBY4BIR_36.webp</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_ROUND_END/2d/</t>
+          <t>public/assets/outdoor-cooking/gas-grills/RUBY4BIR/2d/</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
@@ -11726,36 +11726,36 @@
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Ruby Gas Grills</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ROUND_END</t>
+          <t>RUBY5BIR</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ROUND_END_RIGHT</t>
+          <t>RUBY5BIR_42</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_ROUND_END_RIGHT.webp</t>
+          <t>RUBY5BIR_42.webp</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_ROUND_END/2d/</t>
+          <t>public/assets/outdoor-cooking/gas-grills/RUBY5BIR/2d/</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
@@ -11772,36 +11772,36 @@
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Versa Side Burners</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SAPFR21PRO_BATRIM21_26</t>
+          <t>SUN13CPRO</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SAPFR21PRO_BATRIM21_26</t>
+          <t>SUN13CPRO</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SAPFR21PRO_BATRIM21_26.webp</t>
+          <t>SUN13CPRO.webp</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_SAPFR21PRO_BATRIM21_26/2d/</t>
+          <t>public/assets/outdoor-cooking/side-burners/SUN13CPRO/2d/</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -11818,36 +11818,36 @@
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Versa Side Burners</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SCC3ENDSPL</t>
+          <t>SUN13VDB</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SCC3ENDSPL_LEFT</t>
+          <t>SUN13VDB</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_SCC3ENDSPL_LEFT.webp</t>
+          <t>SUN13VDB.webp</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_SCC3ENDSPL/2d/</t>
+          <t>public/assets/outdoor-cooking/side-burners/SUN13VDB/2d/</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
@@ -11864,36 +11864,36 @@
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>Outdoor Cooking</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Versa Side Burners</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_12</t>
+          <t>SUN13VSB</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_12</t>
+          <t>SUN13VSB</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_12.webp</t>
+          <t>SUN13VSB.webp</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_12/2d/</t>
+          <t>public/assets/outdoor-cooking/side-burners/SUN13VSB/2d/</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -11910,36 +11910,36 @@
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_24</t>
+          <t>A_DD30</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_24</t>
+          <t>A_DD30</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_24.webp</t>
+          <t>A_DD30.webp</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_24/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DD30/2d/</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -11956,36 +11956,36 @@
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_36</t>
+          <t>A_DD36</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_36</t>
+          <t>A_DD36</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_36.webp</t>
+          <t>A_DD36.webp</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_36/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DD36/2d/</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -12002,36 +12002,36 @@
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_48</t>
+          <t>A_DD42</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_48</t>
+          <t>A_DD42</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_48.webp</t>
+          <t>A_DD42.webp</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_48/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DD42/2d/</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
@@ -12048,36 +12048,36 @@
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Straight &amp; Ends</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_OVERHANG_12</t>
+          <t>A_DH1420</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_OVERHANG_12</t>
+          <t>A_DH1420_L</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STRAIGHT_OVERHANG_12.webp</t>
+          <t>A_DH1420_L.webp</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/straight-and-ends/ISLAND_STRAIGHT_OVERHANG_12/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DH1420/2d/</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
@@ -12094,36 +12094,36 @@
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BAR_ROUND_36_STUCCO</t>
+          <t>A_DH1420</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BAR_ROUND_36_STUCCO</t>
+          <t>A_DH1420_R</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_BAR_ROUND_36_STUCCO.webp</t>
+          <t>A_DH1420_R.webp</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_BAR_ROUND_36_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DH1420/2d/</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
@@ -12140,36 +12140,36 @@
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_CORNER_4X4_STUCCO</t>
+          <t>A_DH1724</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_CORNER_4X4_STUCCO</t>
+          <t>A_DH1724_L</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_CORNER_4X4_STUCCO.webp</t>
+          <t>A_DH1724_L.webp</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_CORNER_4X4_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DH1724/2d/</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
@@ -12186,36 +12186,36 @@
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_EXTEND_24_STUCCO</t>
+          <t>A_DH1724</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_EXTEND_24_STUCCO</t>
+          <t>A_DH1724_R</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_EXTEND_24_STUCCO.webp</t>
+          <t>A_DH1724_R.webp</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_EXTEND_24_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DH1724/2d/</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
@@ -12232,36 +12232,36 @@
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_L_6FT_STUCCO</t>
+          <t>A_DV1420</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_L_6FT_STUCCO</t>
+          <t>A_DV1420_L</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_L_6FT_STUCCO.webp</t>
+          <t>A_DV1420_L.webp</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_L_6FT_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DV1420/2d/</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
@@ -12278,36 +12278,36 @@
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_R_6FT_STUCCO</t>
+          <t>A_DV1420</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_R_6FT_STUCCO</t>
+          <t>A_DV1420_R</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_CORONADO_R_6FT_STUCCO.webp</t>
+          <t>A_DV1420_R.webp</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_CORONADO_R_6FT_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DV1420/2d/</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
@@ -12324,36 +12324,36 @@
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_45_ANGLE_STUCCO</t>
+          <t>A_DV1724</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_45_ANGLE_STUCCO</t>
+          <t>A_DV1724_L</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_45_ANGLE_STUCCO.webp</t>
+          <t>A_DV1724_L.webp</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_45_ANGLE_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DV1724/2d/</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
@@ -12370,36 +12370,36 @@
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_CORNER_30x48_STUCCO</t>
+          <t>A_DV1724</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_CORNER_30x48_STUCCO</t>
+          <t>A_DV1724_R</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_CORNER_30x48_STUCCO.webp</t>
+          <t>A_DV1724_R.webp</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_L_CORNER_30x48_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_DV1724/2d/</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
@@ -12416,36 +12416,36 @@
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_LANDING_4FT_STUCCO</t>
+          <t>A_IC</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_LANDING_4FT_STUCCO</t>
+          <t>A_IC</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_LANDING_4FT_STUCCO.webp</t>
+          <t>A_IC.webp</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_L_LANDING_4FT_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_IC/2d/</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
@@ -12462,36 +12462,36 @@
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_ROUND_4FT_STUCCO</t>
+          <t>A_LPCDD30</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_ROUND_4FT_STUCCO</t>
+          <t>A_LPCDD30</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_L_ROUND_4FT_STUCCO.webp</t>
+          <t>A_LPCDD30.webp</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_L_ROUND_4FT_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_LPCDD30/2d/</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
@@ -12508,36 +12508,36 @@
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_CORNER_30x48_STUCCO</t>
+          <t>A_LPCTD30</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_CORNER_30x48_STUCCO</t>
+          <t>A_LPCTD30</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_CORNER_30x48_STUCCO.webp</t>
+          <t>A_LPCTD30.webp</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_R_CORNER_30x48_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_LPCTD30/2d/</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
@@ -12554,36 +12554,36 @@
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_LANDING_4FT_STUCCO</t>
+          <t>A_SS17</t>
         </is>
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_LANDING_4FT_STUCCO</t>
+          <t>A_SS17</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_LANDING_4FT_STUCCO.webp</t>
+          <t>A_SS17.webp</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_R_LANDING_4FT_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_SS17/2d/</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
@@ -12600,36 +12600,36 @@
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_ROUND_4FT_STUCCO</t>
+          <t>A_TRHD</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_ROUND_4FT_STUCCO</t>
+          <t>A_TRHD</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_R_ROUND_4FT_STUCCO.webp</t>
+          <t>A_TRHD.webp</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_R_ROUND_4FT_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/A_TRHD/2d/</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
@@ -12646,36 +12646,36 @@
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_STRAIGHT_24_STUCCO</t>
+          <t>B_DD12</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_STRAIGHT_24_STUCCO</t>
+          <t>B_DD12</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_RAISED_STRAIGHT_24_STUCCO.webp</t>
+          <t>B_DD12.webp</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_RAISED_STRAIGHT_24_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/B_DD12/2d/</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
@@ -12692,36 +12692,36 @@
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STCROIX_8FT_STUCCO</t>
+          <t>B_IC14</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STCROIX_8FT_STUCCO</t>
+          <t>B_IC14</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STCROIX_8FT_STUCCO.webp</t>
+          <t>B_IC14.webp</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STCROIX_8FT_STUCCO/2d/</t>
+          <t>public/assets/odk-components/classic-series/B_IC14/2d/</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
@@ -12738,36 +12738,36 @@
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_CORNER_FIREPLACE</t>
+          <t>B_PS21</t>
         </is>
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_CORNER_FIREPLACE</t>
+          <t>B_PS21</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_CORNER_FIREPLACE.webp</t>
+          <t>B_PS21.webp</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_CORNER_FIREPLACE/2d/</t>
+          <t>public/assets/odk-components/classic-series/B_PS21/2d/</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -12784,36 +12784,36 @@
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_KAMADOBASE_30</t>
+          <t>B_SD6</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_KAMADOBASE_30</t>
+          <t>B_SD6</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_KAMADOBASE_30.webp</t>
+          <t>B_SD6.webp</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_KAMADOBASE_30/2d/</t>
+          <t>public/assets/odk-components/classic-series/B_SD6/2d/</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
@@ -12830,36 +12830,36 @@
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_LOWBASE</t>
+          <t>B_SK20</t>
         </is>
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_LOWBASE_LEFT</t>
+          <t>B_SK20</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_LOWBASE_LEFT.webp</t>
+          <t>B_SK20.webp</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_LOWBASE/2d/</t>
+          <t>public/assets/odk-components/classic-series/B_SK20/2d/</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
@@ -12876,36 +12876,36 @@
     </row>
     <row r="115">
       <c r="A115" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_LOWBASE</t>
+          <t>B_SK34</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_LOWBASE_RIGHT</t>
+          <t>B_SK34</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_LOWBASE_RIGHT.webp</t>
+          <t>B_SK34.webp</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_LOWBASE/2d/</t>
+          <t>public/assets/odk-components/classic-series/B_SK34/2d/</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -12922,36 +12922,36 @@
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_OVERHANG_12</t>
+          <t>B_TD18</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_OVERHANG_12</t>
+          <t>B_TD18</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_OVERHANG_12.webp</t>
+          <t>B_TD18.webp</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_OVERHANG_12/2d/</t>
+          <t>public/assets/odk-components/classic-series/B_TD18/2d/</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -12968,36 +12968,36 @@
     </row>
     <row r="117">
       <c r="A117" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_SCC3ENDSPL</t>
+          <t>C_DD30</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_SCC3ENDSPL_LEFT</t>
+          <t>C_DD30</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_SCC3ENDSPL_LEFT.webp</t>
+          <t>C_DD30.webp</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_SCC3ENDSPL/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_DD30/2d/</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
@@ -13014,36 +13014,36 @@
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Island Modules</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>Stucco / Masonry</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_SCC3ENDSPL</t>
+          <t>C_DD36</t>
         </is>
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_SCC3ENDSPL_RIGHT</t>
+          <t>C_DD36</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>ISLAND_STUCCO_SCC3ENDSPL_RIGHT.webp</t>
+          <t>C_DD36.webp</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>public/assets/island-modules/stucco-masonry/ISLAND_STUCCO_SCC3ENDSPL/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_DD36/2d/</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
@@ -13060,36 +13060,36 @@
     </row>
     <row r="119">
       <c r="A119" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>ADA Compliant Sinks</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>ADASK20</t>
+          <t>C_DD42</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>ADASK20</t>
+          <t>C_DD42</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>ADASK20.webp</t>
+          <t>C_DD42.webp</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/ada-compliant-sinks/ADASK20/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_DD42/2d/</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
@@ -13106,36 +13106,36 @@
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>ADA Compliant Sinks</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>ADASK37</t>
+          <t>C_DDC30</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>ADASK37</t>
+          <t>C_DDC30</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>ADASK37.webp</t>
+          <t>C_DDC30.webp</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/ada-compliant-sinks/ADASK37/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_DDC30/2d/</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
@@ -13152,36 +13152,36 @@
     </row>
     <row r="121">
       <c r="A121" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>Appliance Components</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>BC_BC14</t>
+          <t>C_LPCD20</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>BC_BC14</t>
+          <t>C_LPCD20</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>BC_BC14.webp</t>
+          <t>C_LPCD20.webp</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/appliance-components/BC_BC14/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_LPCD20/2d/</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
@@ -13198,36 +13198,36 @@
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>Appliance Components</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>BC_TD14</t>
+          <t>C_SD12</t>
         </is>
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>BC_TD14</t>
+          <t>C_SD12_L</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>BC_TD14.webp</t>
+          <t>C_SD12_L.webp</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/appliance-components/BC_TD14/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_SD12/2d/</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
@@ -13244,36 +13244,36 @@
     </row>
     <row r="123">
       <c r="A123" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>Appliance Components</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>BRBC14</t>
+          <t>C_SD12</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>BRBC14</t>
+          <t>C_SD12_R</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>BRBC14.webp</t>
+          <t>C_SD12_R.webp</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/appliance-components/BRBC14/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_SD12/2d/</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
@@ -13290,36 +13290,36 @@
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>Refrigeration &amp; Warming</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>SAPFR21PRO</t>
+          <t>C_VSDL12</t>
         </is>
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>SAPFR21PRO</t>
+          <t>C_VSDL12_L</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>SAPFR21PRO.webp</t>
+          <t>C_VSDL12_L.webp</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/refrigeration-warming/SAPFR21PRO/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_VSDL12/2d/</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
@@ -13336,36 +13336,36 @@
     </row>
     <row r="125">
       <c r="A125" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Refrigeration &amp; Warming</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>SAPFR21PRO</t>
+          <t>C_VSDR12</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>SAPFR21PRO_BATRIM21</t>
+          <t>C_VSDR12_R</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>SAPFR21PRO_BATRIM21.webp</t>
+          <t>C_VSDR12_R.webp</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/refrigeration-warming/SAPFR21PRO/2d/</t>
+          <t>public/assets/odk-components/classic-series/C_VSDR12/2d/</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
@@ -13382,36 +13382,36 @@
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Refrigeration &amp; Warming</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>SAPWD30PRO</t>
+          <t>DSH1724</t>
         </is>
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>SAPWD30PRO</t>
+          <t>DSH1724_L</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>SAPWD30PRO.webp</t>
+          <t>DSH1724_L.webp</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/refrigeration-warming/SAPWD30PRO/2d/</t>
+          <t>public/assets/odk-components/classic-series/DSH1724/2d/</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -13428,36 +13428,36 @@
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>Appliances &amp; Sinks</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Refrigeration &amp; Warming</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>SAPWD30PRO</t>
+          <t>DSH1724</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>SAPWD30PRO_DE</t>
+          <t>DSH1724_R</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>SAPWD30PRO_DE.webp</t>
+          <t>DSH1724_R.webp</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>public/assets/appliances/refrigeration-warming/SAPWD30PRO/2d/</t>
+          <t>public/assets/odk-components/classic-series/DSH1724/2d/</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
@@ -13474,36 +13474,36 @@
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>Outdoor Cooking</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Charcoal Combo Grillers</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>SUNCHDZ42</t>
+          <t>DSH30</t>
         </is>
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>SUNCHDZ42</t>
+          <t>DSH30</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>SUNCHDZ42.webp</t>
+          <t>DSH30.webp</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>public/assets/outdoor-cooking/charcoal-combo-grillers/SUNCHDZ42/2d/</t>
+          <t>public/assets/odk-components/classic-series/DSH30/2d/</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
@@ -13520,36 +13520,36 @@
     </row>
     <row r="129">
       <c r="A129" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Outdoor Cooking</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Charcoal Combo Grillers</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>SUNCHSZ30</t>
+          <t>DSV1724</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>SUNCHSZ30</t>
+          <t>DSV1724_L</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>SUNCHSZ30.webp</t>
+          <t>DSV1724_L.webp</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>public/assets/outdoor-cooking/charcoal-combo-grillers/SUNCHSZ30/2d/</t>
+          <t>public/assets/odk-components/classic-series/DSV1724/2d/</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
@@ -13566,36 +13566,36 @@
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>Outdoor Cooking</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>Grill Components</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>VENT</t>
+          <t>DSV1724</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>VENT_GBOX</t>
+          <t>DSV1724_R</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>VENT_GBOX.webp</t>
+          <t>DSV1724_R.webp</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>public/assets/outdoor-cooking/grill-components/VENT/2d/</t>
+          <t>public/assets/odk-components/classic-series/DSV1724/2d/</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -13612,36 +13612,36 @@
     </row>
     <row r="131">
       <c r="A131" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Outdoor Cooking</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>Grill Components</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>VENT</t>
+          <t>DV1420</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>VENT_L</t>
+          <t>DV1420_L</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>VENT_L.webp</t>
+          <t>DV1420_L.webp</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>public/assets/outdoor-cooking/grill-components/VENT/2d/</t>
+          <t>public/assets/odk-components/classic-series/DV1420/2d/</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
@@ -13658,36 +13658,36 @@
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Outdoor Cooking</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>Grill Components</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>VENT</t>
+          <t>DV1420</t>
         </is>
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>VENT_S</t>
+          <t>DV1420_R</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>VENT_S.webp</t>
+          <t>DV1420_R.webp</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>public/assets/outdoor-cooking/grill-components/VENT/2d/</t>
+          <t>public/assets/odk-components/classic-series/DV1420/2d/</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
@@ -13704,36 +13704,36 @@
     </row>
     <row r="133">
       <c r="A133" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Outdoor Cooking</t>
+          <t>ODK Components</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>Pellet Grills</t>
+          <t>Classic Series Flush Style</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>SUNPLT40</t>
+          <t>DV1724</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>SUNPLT40</t>
+          <t>DV1724_L</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>SUNPLT40.webp</t>
+          <t>DV1724_L.webp</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>public/assets/outdoor-cooking/pellet-grills/SUNPLT40/2d/</t>
+          <t>public/assets/odk-components/classic-series/DV1724/2d/</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
@@ -13748,2264 +13748,10 @@
       </c>
       <c r="J133" s="8" t="inlineStr"/>
     </row>
-    <row r="134">
-      <c r="A134" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="inlineStr">
-        <is>
-          <t>Power Cirque Burners &amp; Griddles</t>
-        </is>
-      </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>SUN24PCB</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>SUN24PCB_GD</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>SUN24PCB_GD.webp</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/power-burners-griddles/SUN24PCB/2d/</t>
-        </is>
-      </c>
-      <c r="H134" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I134" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J134" s="8" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr">
-        <is>
-          <t>Power Cirque Burners &amp; Griddles</t>
-        </is>
-      </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>SUN24PCB</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>SUN24PCB_PB</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>SUN24PCB_PB.webp</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/power-burners-griddles/SUN24PCB/2d/</t>
-        </is>
-      </c>
-      <c r="H135" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I135" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J135" s="8" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="inlineStr">
-        <is>
-          <t>Ruby Gas Grills</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>RUBY3B</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>RUBY3B_30</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>RUBY3B_30.webp</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/gas-grills/RUBY3B/2d/</t>
-        </is>
-      </c>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I136" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J136" s="8" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>Ruby Gas Grills</t>
-        </is>
-      </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>RUBY4B</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="inlineStr">
-        <is>
-          <t>RUBY4B_36</t>
-        </is>
-      </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>RUBY4B_36.webp</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/gas-grills/RUBY4B/2d/</t>
-        </is>
-      </c>
-      <c r="H137" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I137" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J137" s="8" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="inlineStr">
-        <is>
-          <t>Ruby Gas Grills</t>
-        </is>
-      </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>RUBY4BIR</t>
-        </is>
-      </c>
-      <c r="E138" s="7" t="inlineStr">
-        <is>
-          <t>RUBY4BIR_36</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="inlineStr">
-        <is>
-          <t>RUBY4BIR_36.webp</t>
-        </is>
-      </c>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/gas-grills/RUBY4BIR/2d/</t>
-        </is>
-      </c>
-      <c r="H138" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I138" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J138" s="8" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>Ruby Gas Grills</t>
-        </is>
-      </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>RUBY5BIR</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>RUBY5BIR_42</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>RUBY5BIR_42.webp</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/gas-grills/RUBY5BIR/2d/</t>
-        </is>
-      </c>
-      <c r="H139" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I139" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J139" s="8" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t>Versa Side Burners</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>SUN13CPRO</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>SUN13CPRO</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>SUN13CPRO.webp</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/side-burners/SUN13CPRO/2d/</t>
-        </is>
-      </c>
-      <c r="H140" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I140" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J140" s="8" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>Versa Side Burners</t>
-        </is>
-      </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>SUN13VDB</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>SUN13VDB</t>
-        </is>
-      </c>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>SUN13VDB.webp</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/side-burners/SUN13VDB/2d/</t>
-        </is>
-      </c>
-      <c r="H141" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I141" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J141" s="8" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>Outdoor Cooking</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="inlineStr">
-        <is>
-          <t>Versa Side Burners</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>SUN13VSB</t>
-        </is>
-      </c>
-      <c r="E142" s="7" t="inlineStr">
-        <is>
-          <t>SUN13VSB</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>SUN13VSB.webp</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/outdoor-cooking/side-burners/SUN13VSB/2d/</t>
-        </is>
-      </c>
-      <c r="H142" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I142" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J142" s="8" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B143" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>A_DD30</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>A_DD30</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>A_DD30.webp</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DD30/2d/</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I143" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J143" s="8" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B144" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C144" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>A_DD36</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr">
-        <is>
-          <t>A_DD36</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>A_DD36.webp</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DD36/2d/</t>
-        </is>
-      </c>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I144" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J144" s="8" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C145" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>A_DD42</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>A_DD42</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>A_DD42.webp</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DD42/2d/</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I145" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J145" s="8" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D146" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1420</t>
-        </is>
-      </c>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1420_L</t>
-        </is>
-      </c>
-      <c r="F146" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1420_L.webp</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DH1420/2d/</t>
-        </is>
-      </c>
-      <c r="H146" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I146" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J146" s="8" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B147" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C147" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1420</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1420_R</t>
-        </is>
-      </c>
-      <c r="F147" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1420_R.webp</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DH1420/2d/</t>
-        </is>
-      </c>
-      <c r="H147" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I147" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J147" s="8" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B148" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C148" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D148" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1724</t>
-        </is>
-      </c>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1724_L</t>
-        </is>
-      </c>
-      <c r="F148" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1724_L.webp</t>
-        </is>
-      </c>
-      <c r="G148" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DH1724/2d/</t>
-        </is>
-      </c>
-      <c r="H148" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I148" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J148" s="8" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B149" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C149" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1724</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1724_R</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>A_DH1724_R.webp</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DH1724/2d/</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I149" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J149" s="8" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B150" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C150" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1420</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1420_L</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1420_L.webp</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DV1420/2d/</t>
-        </is>
-      </c>
-      <c r="H150" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I150" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J150" s="8" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1420</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1420_R</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1420_R.webp</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DV1420/2d/</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I151" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J151" s="8" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1724</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1724_L</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1724_L.webp</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DV1724/2d/</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I152" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J152" s="8" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C153" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D153" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1724</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1724_R</t>
-        </is>
-      </c>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>A_DV1724_R.webp</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_DV1724/2d/</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I153" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J153" s="8" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B154" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C154" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D154" s="7" t="inlineStr">
-        <is>
-          <t>A_IC</t>
-        </is>
-      </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>A_IC</t>
-        </is>
-      </c>
-      <c r="F154" s="7" t="inlineStr">
-        <is>
-          <t>A_IC.webp</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_IC/2d/</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I154" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J154" s="8" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D155" s="7" t="inlineStr">
-        <is>
-          <t>A_LPCDD30</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="inlineStr">
-        <is>
-          <t>A_LPCDD30</t>
-        </is>
-      </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>A_LPCDD30.webp</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_LPCDD30/2d/</t>
-        </is>
-      </c>
-      <c r="H155" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I155" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J155" s="8" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C156" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D156" s="7" t="inlineStr">
-        <is>
-          <t>A_LPCTD30</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>A_LPCTD30</t>
-        </is>
-      </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>A_LPCTD30.webp</t>
-        </is>
-      </c>
-      <c r="G156" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_LPCTD30/2d/</t>
-        </is>
-      </c>
-      <c r="H156" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I156" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J156" s="8" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C157" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D157" s="7" t="inlineStr">
-        <is>
-          <t>A_SS17</t>
-        </is>
-      </c>
-      <c r="E157" s="7" t="inlineStr">
-        <is>
-          <t>A_SS17</t>
-        </is>
-      </c>
-      <c r="F157" s="7" t="inlineStr">
-        <is>
-          <t>A_SS17.webp</t>
-        </is>
-      </c>
-      <c r="G157" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_SS17/2d/</t>
-        </is>
-      </c>
-      <c r="H157" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I157" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J157" s="8" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D158" s="7" t="inlineStr">
-        <is>
-          <t>A_TRHD</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>A_TRHD</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
-        <is>
-          <t>A_TRHD.webp</t>
-        </is>
-      </c>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/A_TRHD/2d/</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I158" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J158" s="8" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D159" s="7" t="inlineStr">
-        <is>
-          <t>B_DD12</t>
-        </is>
-      </c>
-      <c r="E159" s="7" t="inlineStr">
-        <is>
-          <t>B_DD12</t>
-        </is>
-      </c>
-      <c r="F159" s="7" t="inlineStr">
-        <is>
-          <t>B_DD12.webp</t>
-        </is>
-      </c>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/B_DD12/2d/</t>
-        </is>
-      </c>
-      <c r="H159" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I159" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J159" s="8" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D160" s="7" t="inlineStr">
-        <is>
-          <t>B_IC14</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>B_IC14</t>
-        </is>
-      </c>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>B_IC14.webp</t>
-        </is>
-      </c>
-      <c r="G160" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/B_IC14/2d/</t>
-        </is>
-      </c>
-      <c r="H160" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I160" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J160" s="8" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D161" s="7" t="inlineStr">
-        <is>
-          <t>B_PS21</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>B_PS21</t>
-        </is>
-      </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>B_PS21.webp</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/B_PS21/2d/</t>
-        </is>
-      </c>
-      <c r="H161" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I161" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J161" s="8" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D162" s="7" t="inlineStr">
-        <is>
-          <t>B_SD6</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t>B_SD6</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>B_SD6.webp</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/B_SD6/2d/</t>
-        </is>
-      </c>
-      <c r="H162" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I162" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J162" s="8" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C163" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D163" s="7" t="inlineStr">
-        <is>
-          <t>B_SK20</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="inlineStr">
-        <is>
-          <t>B_SK20</t>
-        </is>
-      </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>B_SK20.webp</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/B_SK20/2d/</t>
-        </is>
-      </c>
-      <c r="H163" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I163" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J163" s="8" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B164" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C164" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D164" s="7" t="inlineStr">
-        <is>
-          <t>B_SK34</t>
-        </is>
-      </c>
-      <c r="E164" s="7" t="inlineStr">
-        <is>
-          <t>B_SK34</t>
-        </is>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>B_SK34.webp</t>
-        </is>
-      </c>
-      <c r="G164" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/B_SK34/2d/</t>
-        </is>
-      </c>
-      <c r="H164" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I164" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J164" s="8" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C165" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D165" s="7" t="inlineStr">
-        <is>
-          <t>B_TD18</t>
-        </is>
-      </c>
-      <c r="E165" s="7" t="inlineStr">
-        <is>
-          <t>B_TD18</t>
-        </is>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>B_TD18.webp</t>
-        </is>
-      </c>
-      <c r="G165" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/B_TD18/2d/</t>
-        </is>
-      </c>
-      <c r="H165" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I165" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J165" s="8" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C166" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D166" s="7" t="inlineStr">
-        <is>
-          <t>C_DD30</t>
-        </is>
-      </c>
-      <c r="E166" s="7" t="inlineStr">
-        <is>
-          <t>C_DD30</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>C_DD30.webp</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_DD30/2d/</t>
-        </is>
-      </c>
-      <c r="H166" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I166" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J166" s="8" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>C_DD36</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>C_DD36</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>C_DD36.webp</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_DD36/2d/</t>
-        </is>
-      </c>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I167" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J167" s="8" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C168" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>C_DD42</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>C_DD42</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr">
-        <is>
-          <t>C_DD42.webp</t>
-        </is>
-      </c>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_DD42/2d/</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I168" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J168" s="8" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B169" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C169" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>C_DDC30</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="inlineStr">
-        <is>
-          <t>C_DDC30</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>C_DDC30.webp</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_DDC30/2d/</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I169" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J169" s="8" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C170" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>C_LPCD20</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>C_LPCD20</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>C_LPCD20.webp</t>
-        </is>
-      </c>
-      <c r="G170" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_LPCD20/2d/</t>
-        </is>
-      </c>
-      <c r="H170" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I170" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J170" s="8" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C171" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>C_SD12</t>
-        </is>
-      </c>
-      <c r="E171" s="7" t="inlineStr">
-        <is>
-          <t>C_SD12_L</t>
-        </is>
-      </c>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>C_SD12_L.webp</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_SD12/2d/</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I171" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J171" s="8" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C172" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D172" s="7" t="inlineStr">
-        <is>
-          <t>C_SD12</t>
-        </is>
-      </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>C_SD12_R</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>C_SD12_R.webp</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_SD12/2d/</t>
-        </is>
-      </c>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I172" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J172" s="8" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C173" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D173" s="7" t="inlineStr">
-        <is>
-          <t>C_VSDL12</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="inlineStr">
-        <is>
-          <t>C_VSDL12_L</t>
-        </is>
-      </c>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>C_VSDL12_L.webp</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_VSDL12/2d/</t>
-        </is>
-      </c>
-      <c r="H173" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I173" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J173" s="8" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C174" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D174" s="7" t="inlineStr">
-        <is>
-          <t>C_VSDR12</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="inlineStr">
-        <is>
-          <t>C_VSDR12_R</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr">
-        <is>
-          <t>C_VSDR12_R.webp</t>
-        </is>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/C_VSDR12/2d/</t>
-        </is>
-      </c>
-      <c r="H174" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I174" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J174" s="8" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B175" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C175" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>DSH1724</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>DSH1724_L</t>
-        </is>
-      </c>
-      <c r="F175" s="7" t="inlineStr">
-        <is>
-          <t>DSH1724_L.webp</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DSH1724/2d/</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I175" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J175" s="8" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B176" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C176" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>DSH1724</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>DSH1724_R</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>DSH1724_R.webp</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DSH1724/2d/</t>
-        </is>
-      </c>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I176" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J176" s="8" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C177" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D177" s="7" t="inlineStr">
-        <is>
-          <t>DSH30</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>DSH30</t>
-        </is>
-      </c>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>DSH30.webp</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DSH30/2d/</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I177" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J177" s="8" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C178" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr">
-        <is>
-          <t>DSV1724</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>DSV1724_L</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>DSV1724_L.webp</t>
-        </is>
-      </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DSV1724/2d/</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I178" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J178" s="8" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C179" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>DSV1724</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>DSV1724_R</t>
-        </is>
-      </c>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>DSV1724_R.webp</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DSV1724/2d/</t>
-        </is>
-      </c>
-      <c r="H179" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I179" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J179" s="8" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C180" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
-          <t>DV1420</t>
-        </is>
-      </c>
-      <c r="E180" s="7" t="inlineStr">
-        <is>
-          <t>DV1420_L</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>DV1420_L.webp</t>
-        </is>
-      </c>
-      <c r="G180" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DV1420/2d/</t>
-        </is>
-      </c>
-      <c r="H180" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I180" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J180" s="8" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C181" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D181" s="7" t="inlineStr">
-        <is>
-          <t>DV1420</t>
-        </is>
-      </c>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>DV1420_R</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>DV1420_R.webp</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DV1420/2d/</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I181" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J181" s="8" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>ODK Components</t>
-        </is>
-      </c>
-      <c r="C182" s="7" t="inlineStr">
-        <is>
-          <t>Classic Series Flush Style</t>
-        </is>
-      </c>
-      <c r="D182" s="7" t="inlineStr">
-        <is>
-          <t>DV1724</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>DV1724_L</t>
-        </is>
-      </c>
-      <c r="F182" s="7" t="inlineStr">
-        <is>
-          <t>DV1724_L.webp</t>
-        </is>
-      </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>public/assets/odk-components/classic-series/DV1724/2d/</t>
-        </is>
-      </c>
-      <c r="H182" s="7" t="inlineStr">
-        <is>
-          <t>No 3D model yet</t>
-        </is>
-      </c>
-      <c r="I182" s="7" t="inlineStr">
-        <is>
-          <t>Needs artwork or a 3D model</t>
-        </is>
-      </c>
-      <c r="J182" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:J182"/>
+  <autoFilter ref="A4:J133"/>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J182" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
